--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484708_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484708_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1838</v>
+        <v>6.1586</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6024</v>
+        <v>3.5508</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5814</v>
+        <v>2.6078</v>
       </c>
       <c r="G2" t="n">
         <v>1.0535</v>
@@ -610,13 +610,13 @@
         <v>1.6983</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9981</v>
+        <v>-0.027</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2461</v>
+        <v>0.1945</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.248</v>
+        <v>-0.2215</v>
       </c>
       <c r="V2" t="n">
         <v>3.4338</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.84</v>
+        <v>3.7704</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1291</v>
+        <v>1.3239</v>
       </c>
       <c r="F3" t="n">
-        <v>2.711</v>
+        <v>2.4464</v>
       </c>
       <c r="G3" t="n">
         <v>4.5014</v>
@@ -688,13 +688,13 @@
         <v>1.1322</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4333</v>
+        <v>0.3636</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1023</v>
+        <v>0.0925</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5356</v>
+        <v>0.2711</v>
       </c>
       <c r="V3" t="n">
         <v>0.6036</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0093</v>
+        <v>3.4508</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0735</v>
+        <v>1.9118</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9358</v>
+        <v>1.539</v>
       </c>
       <c r="G4" t="n">
         <v>1.8288</v>
@@ -766,13 +766,13 @@
         <v>1.5096</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3291</v>
+        <v>0.1123</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.0312</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5403</v>
+        <v>0.1435</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8607</v>
+        <v>2.8434</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5386</v>
+        <v>0.3383</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3993</v>
+        <v>2.5051</v>
       </c>
       <c r="G5" t="n">
         <v>2.9951</v>
@@ -844,13 +844,13 @@
         <v>1.887</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4173</v>
+        <v>-0.4346</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2222</v>
+        <v>-0.3453</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1951</v>
+        <v>-0.0893</v>
       </c>
       <c r="V5" t="n">
         <v>0.2828</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>P. MEJIA SERRANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3135</v>
+        <v>1.5024</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2572</v>
+        <v>-0.0761</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0564</v>
+        <v>1.5785</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2091</v>
+        <v>1.557</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5597</v>
+        <v>1.1262</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3506</v>
+        <v>0.4309</v>
       </c>
       <c r="J6" t="n">
-        <v>0.263</v>
+        <v>0.4535</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8303</v>
+        <v>1.062</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5673</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9461000000000001</v>
+        <v>1.1035</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7294</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2167</v>
+        <v>1.0393</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3209</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5096</v>
+        <v>0.7548</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6705</v>
+        <v>0.1531</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1455</v>
+        <v>0.4329</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4749</v>
+        <v>-0.2798</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2452</v>
+        <v>0.9244</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3208</v>
+        <v>0.9244</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. MEJIA SERRANO</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9254</v>
+        <v>0.2892</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3886</v>
+        <v>-1.046</v>
       </c>
       <c r="F7" t="n">
-        <v>1.314</v>
+        <v>1.3352</v>
       </c>
       <c r="G7" t="n">
-        <v>1.557</v>
+        <v>1.8406</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1262</v>
+        <v>1.4815</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4309</v>
+        <v>0.3591</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4535</v>
+        <v>0.4465</v>
       </c>
       <c r="K7" t="n">
         <v>1.062</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.6155</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1035</v>
+        <v>1.3941</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.4195</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0393</v>
+        <v>0.9746</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1322</v>
+        <v>1.1322</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7548</v>
+        <v>2.0757</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4238</v>
+        <v>-0.1932</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1205</v>
+        <v>-0.2092</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5443</v>
+        <v>0.016</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9244</v>
+        <v>-2.4904</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9244</v>
+        <v>-0.3398</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.1506</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4025</v>
+        <v>0.1149</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8596</v>
+        <v>-1.6446</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2621</v>
+        <v>1.7595</v>
       </c>
       <c r="G8" t="n">
         <v>1.1426</v>
@@ -1078,13 +1078,13 @@
         <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2034</v>
+        <v>-0.0842</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1147</v>
+        <v>0.1003</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3181</v>
+        <v>-0.1845</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0391</v>
+        <v>-0.357</v>
       </c>
       <c r="E9" t="n">
-        <v>0.399</v>
+        <v>0.0294</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.36</v>
+        <v>-0.3864</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0145</v>
@@ -1156,13 +1156,13 @@
         <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2422</v>
+        <v>-0.1539</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6525</v>
+        <v>0.2829</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4103</v>
+        <v>-0.4367</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9434</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2059</v>
+        <v>-0.4151</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1178</v>
+        <v>-1.7889</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9119</v>
+        <v>1.3738</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8406</v>
+        <v>1.2091</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4815</v>
+        <v>1.5597</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3591</v>
+        <v>-0.3506</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4465</v>
+        <v>0.263</v>
       </c>
       <c r="K10" t="n">
-        <v>1.062</v>
+        <v>0.8303</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6155</v>
+        <v>-0.5673</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3941</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4195</v>
+        <v>0.7294</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9746</v>
+        <v>0.2167</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1322</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0757</v>
+        <v>1.5096</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6883</v>
+        <v>0.9419</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.281</v>
+        <v>1.0993</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4073</v>
+        <v>-0.1575</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4904</v>
+        <v>-1.2452</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3398</v>
+        <v>-0.3208</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1506</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6924</v>
+        <v>-1.0936</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1016</v>
+        <v>-2.5556</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4092</v>
+        <v>1.4621</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8156</v>
@@ -1312,13 +1312,13 @@
         <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5185</v>
+        <v>0.0804</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5879</v>
+        <v>-0.0419</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0694</v>
+        <v>0.1223</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3018</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.676</v>
+        <v>16.264</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5449999999999986</v>
+        <v>0.04300000000000015</v>
       </c>
       <c r="F12" t="n">
-        <v>16.2211</v>
+        <v>16.221</v>
       </c>
       <c r="G12" t="n">
         <v>14.298</v>
@@ -1381,7 +1381,7 @@
         <v>6.0642</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9435000000000002</v>
+        <v>0.9435</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.2655</v>
@@ -1390,13 +1390,13 @@
         <v>13.209</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1705000000000005</v>
+        <v>0.7584</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9870000000000002</v>
+        <v>1.5748</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8165000000000001</v>
+        <v>-0.8164</v>
       </c>
       <c r="V12" t="n">
         <v>0.2637999999999994</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8225</v>
+        <v>2.6978</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3074</v>
+        <v>2.2356</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5151</v>
+        <v>0.4622</v>
       </c>
       <c r="G13" t="n">
         <v>0.8895999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>0.7548</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8764</v>
+        <v>0.7517</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7847</v>
+        <v>0.7129</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0917</v>
+        <v>0.0388</v>
       </c>
       <c r="V13" t="n">
         <v>1.2452</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1577</v>
+        <v>0.7591</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8236</v>
+        <v>-0.4339</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9813</v>
+        <v>1.193</v>
       </c>
       <c r="G14" t="n">
         <v>0.3627</v>
@@ -1546,13 +1546,13 @@
         <v>0.5661</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7901</v>
+        <v>-0.1887</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5755</v>
+        <v>-0.1858</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2145</v>
+        <v>-0.0029</v>
       </c>
       <c r="V14" t="n">
         <v>0.019</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>E. MORATA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7703</v>
+        <v>-0.4203</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6463</v>
+        <v>-1.3428</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.124</v>
+        <v>0.9225</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3072</v>
+        <v>0.3927</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1557</v>
+        <v>0.8561</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1515</v>
+        <v>-0.4635</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.422</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1057</v>
+        <v>1.4274</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6496</v>
+        <v>-1.8494</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2367</v>
+        <v>0.8146</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2614</v>
+        <v>-0.5713</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4981</v>
+        <v>1.3859</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9435</v>
+        <v>0.7548</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0235</v>
+        <v>-0.1377</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1023</v>
+        <v>0.0227</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1259</v>
+        <v>-0.1604</v>
       </c>
       <c r="V15" t="n">
         <v>-1.4301</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. MORATA</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-0.6283</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4402</v>
+        <v>-0.4514</v>
       </c>
       <c r="F16" t="n">
-        <v>0.605</v>
+        <v>-0.1769</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3927</v>
+        <v>-0.3072</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8561</v>
+        <v>-0.1557</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4635</v>
+        <v>-0.1515</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.422</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4274</v>
+        <v>0.1057</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.8494</v>
+        <v>-0.6496</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8146</v>
+        <v>0.2367</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5713</v>
+        <v>-0.2614</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3859</v>
+        <v>0.4981</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7548</v>
+        <v>0.9435</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6983</v>
+        <v>0.9435</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5526</v>
+        <v>0.1655</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.07480000000000001</v>
+        <v>0.0925</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4778</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-1.4301</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9472</v>
+        <v>-1.0266</v>
       </c>
       <c r="E17" t="n">
         <v>-1.6821</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7349</v>
+        <v>0.6555</v>
       </c>
       <c r="G17" t="n">
         <v>-1.4357</v>
@@ -1780,13 +1780,13 @@
         <v>1.1322</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2998</v>
+        <v>0.2205</v>
       </c>
       <c r="T17" t="n">
         <v>0.3926</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.1722</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0666</v>
+        <v>-1.2174</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2939</v>
+        <v>-0.7736</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.4438</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5163</v>
+        <v>-1.4176</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5854</v>
+        <v>-1.062</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.3557</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6496</v>
+        <v>0.112</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6496</v>
+        <v>-0.6807</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8668</v>
+        <v>-1.5297</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5854</v>
+        <v>-1.8547</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2814</v>
+        <v>0.325</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1887</v>
+        <v>1.887</v>
       </c>
       <c r="S18" t="n">
-        <v>0.261</v>
+        <v>-0.2375</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3556</v>
+        <v>0.0769</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0946</v>
+        <v>-0.3144</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.4377</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.4867</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. MARCO CLIMENT</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0784</v>
+        <v>-1.2736</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2513</v>
+        <v>-0.6837</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1729</v>
+        <v>-0.5899</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4615</v>
+        <v>-1.5163</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.6094</v>
+        <v>-0.5854</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1478</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1216</v>
+        <v>-0.6496</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.0958</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9742</v>
+        <v>-0.6496</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3399</v>
+        <v>-0.8668</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5135</v>
+        <v>-0.5854</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1736</v>
+        <v>-0.2814</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1322</v>
+        <v>0.1887</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6983</v>
+        <v>0.1887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7948</v>
+        <v>0.0541</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2047</v>
+        <v>-0.0341</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.0882</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7206</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9054</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1849</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4996</v>
+        <v>-1.3131</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4236</v>
+        <v>-1.1313</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.076</v>
+        <v>-0.1818</v>
       </c>
       <c r="G20" t="n">
         <v>0.1052</v>
@@ -2014,13 +2014,13 @@
         <v>0.5661</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2839</v>
+        <v>-0.0974</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2816</v>
+        <v>0.0107</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0023</v>
+        <v>-0.1081</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MARTINEZ JURADO</t>
+          <t>F. MARCO CLIMENT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4159</v>
+        <v>-1.5569</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1345</v>
+        <v>-2.2513</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2814</v>
+        <v>0.6944</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-1.4615</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9908</v>
+        <v>-3.6094</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2383</v>
+        <v>2.1478</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.1216</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2583</v>
+        <v>-2.0958</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6496</v>
+        <v>1.9742</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1553</v>
+        <v>-1.3399</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7325</v>
+        <v>-1.5135</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8878</v>
+        <v>0.1736</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1887</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7548</v>
+        <v>1.6983</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.89</v>
+        <v>0.3163</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.585</v>
+        <v>-0.2047</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.305</v>
+        <v>0.5209</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5846</v>
+        <v>0.7206</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3018</v>
+        <v>0.9054</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8865</v>
+        <v>-0.1849</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>D. MARTINEZ JURADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8605</v>
+        <v>-2.1175</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9428</v>
+        <v>-1.9396</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9176</v>
+        <v>-0.1779</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4176</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.062</v>
+        <v>-0.9908</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3557</v>
+        <v>0.2383</v>
       </c>
       <c r="J22" t="n">
-        <v>0.112</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7927999999999999</v>
+        <v>-0.2583</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6807</v>
+        <v>-0.6496</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5297</v>
+        <v>0.1553</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8547</v>
+        <v>-0.7325</v>
       </c>
       <c r="O22" t="n">
-        <v>0.325</v>
+        <v>0.8878</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R22" t="n">
-        <v>1.887</v>
+        <v>0.7548</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8805</v>
+        <v>-0.5917</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0923</v>
+        <v>-0.3901</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7882</v>
+        <v>-0.2016</v>
       </c>
       <c r="V22" t="n">
-        <v>0.4377</v>
+        <v>-0.5846</v>
       </c>
       <c r="W22" t="n">
-        <v>0.9244</v>
+        <v>0.3018</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.4867</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.182499999999999</v>
+        <v>-8.832100000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.89</v>
+        <v>-7.6694</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2926</v>
+        <v>-1.1626</v>
       </c>
       <c r="G23" t="n">
         <v>-9.157299999999999</v>
@@ -2248,13 +2248,13 @@
         <v>2.0757</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9711</v>
+        <v>0.3215</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1997</v>
+        <v>0.4202</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2286</v>
+        <v>-0.0987</v>
       </c>
       <c r="V23" t="n">
         <v>0.7585</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.676</v>
+        <v>-14.9289</v>
       </c>
       <c r="E24" t="n">
-        <v>-16.2209</v>
+        <v>-16.1235</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5448999999999997</v>
+        <v>1.1947</v>
       </c>
       <c r="G24" t="n">
         <v>-14.2979</v>
@@ -2326,13 +2326,13 @@
         <v>12.2655</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1705000000000004</v>
+        <v>0.5766000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8164</v>
+        <v>0.9138000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9867</v>
+        <v>-0.3375</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2638</v>
